--- a/app/data/faq.xlsx
+++ b/app/data/faq.xlsx
@@ -1,15 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView windowWidth="23040" windowHeight="8675"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -25,64 +38,22 @@
     <t>ما هي الخدمات التي يقدمها مختبر وريد؟</t>
   </si>
   <si>
+    <t>يقدم مختبر وريد مجموعة واسعة من التحاليل الطبية تشمل: تحاليل الدم الشاملة، الهرمونات، المناعة، الفيتامينات، وظائف الكبد والكلى، الدهون، مؤشرات الالتهاب، فحوصات ما قبل الزواج، فحوصات الأمراض المعدية، إضافة إلى الباقات الصحية الموسمية والباقات المخفضة والتحاليل التخصصية الدقيقة.</t>
+  </si>
+  <si>
     <t>هل يوفر مختبر وريد خدمة الزيارات المنزلية؟</t>
   </si>
   <si>
+    <t>نعم، يوفر مختبر وريد خدمة سحب العينات من المنزل أو مقر العمل مع الالتزام بمعايير التعقيم، وضمان سرعة ظهور النتائج، وتتوفر الخدمة في أغلب المدن التي يتواجد فيها المختبر.</t>
+  </si>
+  <si>
     <t>كم تستغرق نتائج التحاليل للظهور؟</t>
   </si>
   <si>
+    <t>تعتمد مدة ظهور النتائج على نوع التحليل، لكن أغلب التحاليل الأساسية تظهر خلال 12–24 ساعة، بينما بعض التحاليل التخصصية قد تحتاج وقتًا إضافيًا حسب نوع العينة وإجراءات التجهيز.</t>
+  </si>
+  <si>
     <t>ما هي التحاليل التي تحتاج إلى صيام؟</t>
-  </si>
-  <si>
-    <t>هل يقدم مختبر وريد باقات وعروض تحاليل مخفضة؟</t>
-  </si>
-  <si>
-    <t>هل يتم إرسال النتائج إلكترونيًا؟</t>
-  </si>
-  <si>
-    <t>ما هي طرق الدفع المتاحة؟</t>
-  </si>
-  <si>
-    <t>هل التحاليل آمنة للأطفال وكبار السن؟</t>
-  </si>
-  <si>
-    <t>هل يوجد استشارة طبية بعد ظهور النتائج؟</t>
-  </si>
-  <si>
-    <t>أين تتواجد فروع مختبرات وريد؟</t>
-  </si>
-  <si>
-    <t>هل توجد عروض أو تخفيضات حالياً؟</t>
-  </si>
-  <si>
-    <t>كيف أعرف إذا كان هناك عرض قديم ما زال ساريًا؟</t>
-  </si>
-  <si>
-    <t>هل نتائج التحاليل سرية؟</t>
-  </si>
-  <si>
-    <t>كيف يتم ضمان خصوصية التحاليل الحساسة مثل الهرمونات أو الأمراض المزمنة؟</t>
-  </si>
-  <si>
-    <t>ما هي التحاليل المجانية التي يقدمها مختبر وريد؟</t>
-  </si>
-  <si>
-    <t>هل تحليل السكر التراكمي يحتاج صيام؟</t>
-  </si>
-  <si>
-    <t>ما هو رمز تحليل السكر التراكمي؟</t>
-  </si>
-  <si>
-    <t>هل تحليل الغدة الدرقية يحتاج صيام؟</t>
-  </si>
-  <si>
-    <t>يقدم مختبر وريد مجموعة واسعة من التحاليل الطبية تشمل: تحاليل الدم الشاملة، الهرمونات، المناعة، الفيتامينات، وظائف الكبد والكلى، الدهون، مؤشرات الالتهاب، فحوصات ما قبل الزواج، فحوصات الأمراض المعدية، إضافة إلى الباقات الصحية الموسمية والباقات المخفضة والتحاليل التخصصية الدقيقة.</t>
-  </si>
-  <si>
-    <t>نعم، يوفر مختبر وريد خدمة سحب العينات من المنزل أو مقر العمل مع الالتزام بمعايير التعقيم، وضمان سرعة ظهور النتائج، وتتوفر الخدمة في أغلب المدن التي يتواجد فيها المختبر.</t>
-  </si>
-  <si>
-    <t>تعتمد مدة ظهور النتائج على نوع التحليل، لكن أغلب التحاليل الأساسية تظهر خلال 12–24 ساعة، بينما بعض التحاليل التخصصية قد تحتاج وقتًا إضافيًا حسب نوع العينة وإجراءات التجهيز.</t>
   </si>
   <si>
     <t>تتطلب بعض التحاليل صيامًا من 8 إلى 12 ساعة لضمان دقة النتائج، ومن أهمها:
@@ -102,7 +73,13 @@
 - فحوصات المناعة والفيروسات</t>
   </si>
   <si>
+    <t>هل يقدم مختبر وريد باقات وعروض تحاليل مخفضة؟</t>
+  </si>
+  <si>
     <t>نعم، يوفر المختبر باقات موسمية وعروضًا دورية تشمل باقات الفحوصات الشاملة، المناعة، الفيتامينات، والشتوية وغيرها. وتختلف العروض بشكل مستمر، لذلك يُنصح دائمًا بمتابعة صفحة العروض الرسمية أو التواصل مع خدمة العملاء لمعرفة أحدث الباقات المتاحة.</t>
+  </si>
+  <si>
+    <t>هل يتم إرسال النتائج إلكترونيًا؟</t>
   </si>
   <si>
     <t>نعم، يمكنك الحصول على النتائج عبر:
@@ -112,18 +89,33 @@
 دون الحاجة للعودة للمركز.</t>
   </si>
   <si>
+    <t>ما هي طرق الدفع المتاحة؟</t>
+  </si>
+  <si>
     <t>يوفر مختبر وريد خيارات دفع مرنة تشمل: الدفع النقدي، البطاقة البنكية، التحويل البنكي، والدفع الإلكتروني، وتمارا.</t>
   </si>
   <si>
+    <t>هل التحاليل آمنة للأطفال وكبار السن؟</t>
+  </si>
+  <si>
     <t>نعم، يتم إجراء التحاليل باستخدام معدات معقمة وأدوات مخصصة لكل فئة عمرية، مع مراعاة أعلى معايير الأمان والسلامة.</t>
   </si>
   <si>
+    <t>هل يوجد استشارة طبية بعد ظهور النتائج؟</t>
+  </si>
+  <si>
     <t>نعم، يمكن ترتيب استشارة طبية لتفسير النتائج بناءً على طلب العميل، لضمان فهم دقيق لحالته الصحية.</t>
+  </si>
+  <si>
+    <t>أين تتواجد فروع مختبرات وريد؟</t>
   </si>
   <si>
     <t>يتواجد مختبر وريد في أكثر من 60 فرعًا حول المملكة تشمل: الرياض – جدة – الشرقية – المدينة – الجنوب – القصيم – الطائف – تبوك – حائل – والمزيد.
 يمكنك التأكد من جميع الفروع من خلال صفحة الفروع:
 https://wareed.com.sa/our-branches/</t>
+  </si>
+  <si>
+    <t>هل توجد عروض أو تخفيضات حالياً؟</t>
   </si>
   <si>
     <t>نعم، يقدم مختبر وريد عروضاً وباقات مختلفة تتغير بحسب الفترة، وتشمل خصومات موسمية قوية مثل الباقة الشتوية الشاملة وباقات المناعة وغيرها من العروض التي تحظى بإقبال كبير.
@@ -133,17 +125,29 @@
 - التواصل مع خدمة العملاء.</t>
   </si>
   <si>
+    <t>كيف أعرف إذا كان هناك عرض قديم ما زال ساريًا؟</t>
+  </si>
+  <si>
     <t>زيارة صفحة العروض المحدثة في موقع مختبر وريد.
 التحقق من تطبيق المختبر.
 التواصل مع خدمة العملاء للتأكد بشكل نهائي إذا كان العرض ما زال ساريًا.</t>
   </si>
   <si>
+    <t>هل نتائج التحاليل سرية؟</t>
+  </si>
+  <si>
     <t>نعم، جميع التحاليل في مختبر وريد تتمتع بأعلى مستويات السرية والخصوصية.
 يتم حفظ النتائج ضمن نظام آمن ولا يتم الاطلاع عليها إلا من قبل المختصين المخولين بذلك، ولا تُسلَّم لأي شخص آخر إلا بموافقة العميل نفسه.</t>
   </si>
   <si>
+    <t>كيف يتم ضمان خصوصية التحاليل الحساسة مثل الهرمونات أو الأمراض المزمنة؟</t>
+  </si>
+  <si>
     <t>يعتمد مختبر وريد نظام إدارة بيانات مشفّر يضمن حماية المعلومات الحساسة وعدم مشاركتها مع أي جهة خارجية.
 كما يتم تسليم نتائج التحاليل الحساسة مباشرة للعميل عبر طرق آمنة مثل التطبيق الرسمي، الواتساب المسجّل باسم العميل، أو الاستلام الشخصي من الفرع.</t>
+  </si>
+  <si>
+    <t>ما هي التحاليل المجانية التي يقدمها مختبر وريد؟</t>
   </si>
   <si>
     <t>يقدم مختبر وريد مجموعة من الفحوصات المجانية للمراجعين، وتشمل:
@@ -151,11 +155,20 @@
 - 3 تحاليل مجانية بالتعاون مع تطبيق صحتي: الكوليسترول، سكر الدم الصائم (FBS)، الدهون الثلاثية (Triglycerides).</t>
   </si>
   <si>
+    <t>هل تحليل السكر التراكمي يحتاج صيام؟</t>
+  </si>
+  <si>
     <t>لا، تحليل السكر التراكمي (HbA1c) لا يحتاج إلى صيام.
 يقيس متوسط مستوى السكر في الدم خلال آخر 2–3 أشهر ويمكن إجراؤه في أي وقت من اليوم.</t>
   </si>
   <si>
+    <t>ما هو رمز تحليل السكر التراكمي؟</t>
+  </si>
+  <si>
     <t>رمز تحليل السكر التراكمي هو HbA1c، ويُعطي فكرة عن متوسط نسبة السكر في الدم خلال الأشهر الثلاثة الأخيرة، ويساعد الأطباء على متابعة التحكم في مرض السكري.</t>
+  </si>
+  <si>
+    <t>هل تحليل الغدة الدرقية يحتاج صيام؟</t>
   </si>
   <si>
     <t>عادةً تحليل الغدة الدرقية (TSH، FT4، FT3) لا يتطلب صيامًا، ويمكن إجراؤه في أي وقت من اليوم، مع تفضيل أخذ التحليل في الصباح أحيانًا حسب تعليمات الطبيب.</t>
@@ -164,13 +177,19 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -178,19 +197,356 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -213,9 +569,251 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -223,11 +821,63 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -510,14 +1160,18 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
+  <cols>
+    <col min="1" max="1" width="30.3333333333333" customWidth="1"/>
+    <col min="2" max="2" width="49.3333333333333" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
@@ -532,140 +1186,140 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="B19" t="s">
         <v>37</v>
@@ -673,5 +1327,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>